--- a/scripts/simulations/resultados_simulacion/Grupo3_Mezclas/mse_puntual_mezcla_mw_n60.xlsx
+++ b/scripts/simulations/resultados_simulacion/Grupo3_Mezclas/mse_puntual_mezcla_mw_n60.xlsx
@@ -410,20 +410,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="E2">
-        <v>0.003080188422601289</v>
+        <v>0.0005863333003319213</v>
       </c>
       <c r="F2">
-        <v>0.002626032341799054</v>
+        <v>0.0009076490791141256</v>
       </c>
       <c r="G2">
-        <v>0.002250763775500987</v>
+        <v>0.0008605021741789254</v>
       </c>
       <c r="H2">
-        <v>0.003752196416688465</v>
+        <v>0.0005078998653122148</v>
       </c>
     </row>
     <row r="3">
@@ -440,20 +440,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Moda_Izq</t>
         </is>
       </c>
       <c r="E3">
-        <v>0.0005863333003319213</v>
+        <v>0.003089585298309074</v>
       </c>
       <c r="F3">
-        <v>0.0009076490791141256</v>
+        <v>0.002905664789020357</v>
       </c>
       <c r="G3">
-        <v>0.0008605021741789254</v>
+        <v>0.002198860852422067</v>
       </c>
       <c r="H3">
-        <v>0.0005078998653122148</v>
+        <v>0.003772946758377095</v>
       </c>
     </row>
     <row r="4">
@@ -470,20 +470,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Valle_Central</t>
         </is>
       </c>
       <c r="E4">
-        <v>0.003089617194192369</v>
+        <v>0.002059369381090742</v>
       </c>
       <c r="F4">
-        <v>0.002905609084637608</v>
+        <v>0.001327803520081574</v>
       </c>
       <c r="G4">
-        <v>0.002198865082917112</v>
+        <v>0.001170301989639346</v>
       </c>
       <c r="H4">
-        <v>0.003772990483067081</v>
+        <v>0.002702629538561085</v>
       </c>
     </row>
     <row r="5">
@@ -500,20 +500,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Moda_Der</t>
         </is>
       </c>
       <c r="E5">
-        <v>0.002059369381090741</v>
+        <v>0.003080188422601289</v>
       </c>
       <c r="F5">
-        <v>0.001327803520081574</v>
+        <v>0.002626032341799054</v>
       </c>
       <c r="G5">
-        <v>0.001170301989639345</v>
+        <v>0.002250763775500987</v>
       </c>
       <c r="H5">
-        <v>0.002702629538561085</v>
+        <v>0.003752196416688465</v>
       </c>
     </row>
     <row r="6">
@@ -590,20 +590,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>Garra_1</t>
         </is>
       </c>
       <c r="E8">
-        <v>0.04712422617297057</v>
+        <v>0.06342668475102523</v>
       </c>
       <c r="F8">
-        <v>0.04625598941186882</v>
+        <v>0.05718750143666842</v>
       </c>
       <c r="G8">
-        <v>0.04991583883434787</v>
+        <v>0.06269144107767216</v>
       </c>
       <c r="H8">
-        <v>0.08904505823327891</v>
+        <v>0.08541670247217835</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Garra_2</t>
         </is>
       </c>
       <c r="E9">
-        <v>0.01012596509139295</v>
+        <v>0.04549617439506946</v>
       </c>
       <c r="F9">
-        <v>0.008742173980983042</v>
+        <v>0.04768540469051402</v>
       </c>
       <c r="G9">
-        <v>0.01006496804914516</v>
+        <v>0.04684125012267418</v>
       </c>
       <c r="H9">
-        <v>0.009670185392563407</v>
+        <v>0.08609024297039682</v>
       </c>
     </row>
     <row r="10">
@@ -650,20 +650,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Garra_3</t>
         </is>
       </c>
       <c r="E10">
-        <v>0.005444823121725058</v>
+        <v>0.04712422617297048</v>
       </c>
       <c r="F10">
-        <v>0.01316055336346</v>
+        <v>0.04625598941186892</v>
       </c>
       <c r="G10">
-        <v>0.006196655179257763</v>
+        <v>0.04991583883434775</v>
       </c>
       <c r="H10">
-        <v>0.01448721910197803</v>
+        <v>0.08904505823327892</v>
       </c>
     </row>
     <row r="11">
@@ -680,20 +680,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Garra_4</t>
         </is>
       </c>
       <c r="E11">
-        <v>0.04712422617297048</v>
+        <v>0.0484417911684343</v>
       </c>
       <c r="F11">
-        <v>0.04625598941186892</v>
+        <v>0.04942299324934016</v>
       </c>
       <c r="G11">
-        <v>0.04991583883434775</v>
+        <v>0.04968232862771041</v>
       </c>
       <c r="H11">
-        <v>0.08904505823327892</v>
+        <v>0.08667695039302452</v>
       </c>
     </row>
     <row r="12">
@@ -710,20 +710,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Garra_5</t>
         </is>
       </c>
       <c r="E12">
-        <v>0.005487292916759572</v>
+        <v>0.06349706101026741</v>
       </c>
       <c r="F12">
-        <v>0.01248447604930786</v>
+        <v>0.05738353871785867</v>
       </c>
       <c r="G12">
-        <v>0.00605612168492902</v>
+        <v>0.0622742811072768</v>
       </c>
       <c r="H12">
-        <v>0.01463919672188169</v>
+        <v>0.08542214934115094</v>
       </c>
     </row>
     <row r="13">
@@ -770,20 +770,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="E14">
-        <v>0.003352790275471308</v>
+        <v>0.0008778846258405223</v>
       </c>
       <c r="F14">
-        <v>0.003203733641226019</v>
+        <v>0.001296134820316115</v>
       </c>
       <c r="G14">
-        <v>0.00254144392686686</v>
+        <v>0.00123230824248291</v>
       </c>
       <c r="H14">
-        <v>0.004135405630705553</v>
+        <v>0.0007596690741576382</v>
       </c>
     </row>
     <row r="15">
@@ -800,20 +800,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Moda_Izq</t>
         </is>
       </c>
       <c r="E15">
-        <v>0.0008778846258405223</v>
+        <v>0.003197512259607744</v>
       </c>
       <c r="F15">
-        <v>0.001296134820316115</v>
+        <v>0.003052229996646714</v>
       </c>
       <c r="G15">
-        <v>0.00123230824248291</v>
+        <v>0.002499043022925633</v>
       </c>
       <c r="H15">
-        <v>0.0007596690741576382</v>
+        <v>0.003845602048276227</v>
       </c>
     </row>
     <row r="16">
@@ -830,20 +830,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Valle_Central</t>
         </is>
       </c>
       <c r="E16">
-        <v>0.003197568413031467</v>
+        <v>0.001952072547094352</v>
       </c>
       <c r="F16">
-        <v>0.003052224523817006</v>
+        <v>0.001186008029040344</v>
       </c>
       <c r="G16">
-        <v>0.002499093025820506</v>
+        <v>0.001029185514475166</v>
       </c>
       <c r="H16">
-        <v>0.003845665603680118</v>
+        <v>0.002659346573469911</v>
       </c>
     </row>
     <row r="17">
@@ -860,20 +860,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Moda_Der</t>
         </is>
       </c>
       <c r="E17">
-        <v>0.001952072547094352</v>
+        <v>0.003352790275471308</v>
       </c>
       <c r="F17">
-        <v>0.001186008029040343</v>
+        <v>0.003203733641226019</v>
       </c>
       <c r="G17">
-        <v>0.001029185514475166</v>
+        <v>0.00254144392686686</v>
       </c>
       <c r="H17">
-        <v>0.002659346573469909</v>
+        <v>0.004135405630705553</v>
       </c>
     </row>
     <row r="18">
@@ -950,20 +950,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>Garra_1</t>
         </is>
       </c>
       <c r="E20">
-        <v>0.04710702678474558</v>
+        <v>0.06537726034499158</v>
       </c>
       <c r="F20">
-        <v>0.04696610168213693</v>
+        <v>0.0611800246697776</v>
       </c>
       <c r="G20">
-        <v>0.04965542382231098</v>
+        <v>0.06456225388277069</v>
       </c>
       <c r="H20">
-        <v>0.08900224083097218</v>
+        <v>0.08559693440248491</v>
       </c>
     </row>
     <row r="21">
@@ -980,20 +980,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Garra_2</t>
         </is>
       </c>
       <c r="E21">
-        <v>0.01083087700991163</v>
+        <v>0.04820421433247608</v>
       </c>
       <c r="F21">
-        <v>0.009531994971006288</v>
+        <v>0.04995495803133775</v>
       </c>
       <c r="G21">
-        <v>0.01091928729455195</v>
+        <v>0.04940334836912424</v>
       </c>
       <c r="H21">
-        <v>0.009733848998460311</v>
+        <v>0.08647801642336868</v>
       </c>
     </row>
     <row r="22">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Garra_3</t>
         </is>
       </c>
       <c r="E22">
-        <v>0.00651256876726721</v>
+        <v>0.0471070267847457</v>
       </c>
       <c r="F22">
-        <v>0.01315789386046327</v>
+        <v>0.046966101682137</v>
       </c>
       <c r="G22">
-        <v>0.007064018833462673</v>
+        <v>0.04965542382231101</v>
       </c>
       <c r="H22">
-        <v>0.01481557930325607</v>
+        <v>0.08900224083097218</v>
       </c>
     </row>
     <row r="23">
@@ -1040,20 +1040,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Garra_4</t>
         </is>
       </c>
       <c r="E23">
-        <v>0.0471070267847457</v>
+        <v>0.0481402883844738</v>
       </c>
       <c r="F23">
-        <v>0.046966101682137</v>
+        <v>0.05232709666745814</v>
       </c>
       <c r="G23">
-        <v>0.04965542382231101</v>
+        <v>0.04977806158847448</v>
       </c>
       <c r="H23">
-        <v>0.08900224083097218</v>
+        <v>0.08631203526606859</v>
       </c>
     </row>
     <row r="24">
@@ -1070,20 +1070,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Garra_5</t>
         </is>
       </c>
       <c r="E24">
-        <v>0.006522183986361104</v>
+        <v>0.06473503617648833</v>
       </c>
       <c r="F24">
-        <v>0.0136839792010551</v>
+        <v>0.06023952237422107</v>
       </c>
       <c r="G24">
-        <v>0.007169600627564518</v>
+        <v>0.06394283039619157</v>
       </c>
       <c r="H24">
-        <v>0.01472933944034185</v>
+        <v>0.08484170462778111</v>
       </c>
     </row>
     <row r="25">
@@ -1130,20 +1130,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="E26">
-        <v>0.008652898362708982</v>
+        <v>0.004862241945747851</v>
       </c>
       <c r="F26">
-        <v>0.00954162949930026</v>
+        <v>0.006704355265539277</v>
       </c>
       <c r="G26">
-        <v>0.009196964942927127</v>
+        <v>0.006058077243269878</v>
       </c>
       <c r="H26">
-        <v>0.007431114461363634</v>
+        <v>0.00373726277269179</v>
       </c>
     </row>
     <row r="27">
@@ -1160,20 +1160,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Moda_Izq</t>
         </is>
       </c>
       <c r="E27">
-        <v>0.004862241945747851</v>
+        <v>0.008630761898752209</v>
       </c>
       <c r="F27">
-        <v>0.006704355265539277</v>
+        <v>0.0096710001757573</v>
       </c>
       <c r="G27">
-        <v>0.006058077243269878</v>
+        <v>0.009220720546404406</v>
       </c>
       <c r="H27">
-        <v>0.00373726277269179</v>
+        <v>0.00775508396052219</v>
       </c>
     </row>
     <row r="28">
@@ -1190,20 +1190,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Valle_Central</t>
         </is>
       </c>
       <c r="E28">
-        <v>0.008631343861228291</v>
+        <v>0.002173005076624755</v>
       </c>
       <c r="F28">
-        <v>0.009671725287664835</v>
+        <v>0.001606808851911682</v>
       </c>
       <c r="G28">
-        <v>0.009221343054327093</v>
+        <v>0.00150113890557036</v>
       </c>
       <c r="H28">
-        <v>0.007755294965446522</v>
+        <v>0.003439129260117528</v>
       </c>
     </row>
     <row r="29">
@@ -1220,20 +1220,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Moda_Der</t>
         </is>
       </c>
       <c r="E29">
-        <v>0.002173005076624755</v>
+        <v>0.008652898362708982</v>
       </c>
       <c r="F29">
-        <v>0.001606808851911681</v>
+        <v>0.00954162949930026</v>
       </c>
       <c r="G29">
-        <v>0.001501138905570359</v>
+        <v>0.009196964942927127</v>
       </c>
       <c r="H29">
-        <v>0.003439129260117527</v>
+        <v>0.007431114461363634</v>
       </c>
     </row>
     <row r="30">
@@ -1310,20 +1310,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>Garra_1</t>
         </is>
       </c>
       <c r="E32">
-        <v>0.05851955777981292</v>
+        <v>0.0932047825238851</v>
       </c>
       <c r="F32">
-        <v>0.070579318718156</v>
+        <v>0.12546573492803</v>
       </c>
       <c r="G32">
-        <v>0.06265180882957266</v>
+        <v>0.1035263486930977</v>
       </c>
       <c r="H32">
-        <v>0.08667163021046324</v>
+        <v>0.0872731332748628</v>
       </c>
     </row>
     <row r="33">
@@ -1340,20 +1340,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Garra_2</t>
         </is>
       </c>
       <c r="E33">
-        <v>0.0272373064118111</v>
+        <v>0.06411173685821597</v>
       </c>
       <c r="F33">
-        <v>0.02245742564388287</v>
+        <v>0.07779807456421857</v>
       </c>
       <c r="G33">
-        <v>0.026522785056695</v>
+        <v>0.06956974802112807</v>
       </c>
       <c r="H33">
-        <v>0.01391832955887536</v>
+        <v>0.08545842328491417</v>
       </c>
     </row>
     <row r="34">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Garra_3</t>
         </is>
       </c>
       <c r="E34">
-        <v>0.02883189286611621</v>
+        <v>0.05851955777981284</v>
       </c>
       <c r="F34">
-        <v>0.04382129267874459</v>
+        <v>0.07057931871815677</v>
       </c>
       <c r="G34">
-        <v>0.03247077139333667</v>
+        <v>0.06265180882957265</v>
       </c>
       <c r="H34">
-        <v>0.01688695116078837</v>
+        <v>0.08667163021046315</v>
       </c>
     </row>
     <row r="35">
@@ -1400,20 +1400,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Garra_4</t>
         </is>
       </c>
       <c r="E35">
-        <v>0.05851955777981284</v>
+        <v>0.06756169867899404</v>
       </c>
       <c r="F35">
-        <v>0.07057931871815677</v>
+        <v>0.07954437881563356</v>
       </c>
       <c r="G35">
-        <v>0.06265180882957265</v>
+        <v>0.06940129638876966</v>
       </c>
       <c r="H35">
-        <v>0.08667163021046315</v>
+        <v>0.08701599961714719</v>
       </c>
     </row>
     <row r="36">
@@ -1430,20 +1430,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Garra_5</t>
         </is>
       </c>
       <c r="E36">
-        <v>0.02930718272586642</v>
+        <v>0.0934460634882948</v>
       </c>
       <c r="F36">
-        <v>0.04045083094288152</v>
+        <v>0.1129752285687342</v>
       </c>
       <c r="G36">
-        <v>0.03132010209883421</v>
+        <v>0.09904005185441046</v>
       </c>
       <c r="H36">
-        <v>0.0176523696940504</v>
+        <v>0.08830740009725277</v>
       </c>
     </row>
     <row r="37">
